--- a/outputs/evaluation/requirement/design/v1/CF_M05/third/CF_M05_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v1/CF_M05/third/CF_M05_req_eval.xlsx
@@ -548,10 +548,10 @@
         <v>0.9167</v>
       </c>
       <c r="C13" t="n">
+        <v>0.8462</v>
+      </c>
+      <c r="D13" t="n">
         <v>0.88</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.898</v>
       </c>
       <c r="E13" t="n">
         <v>0.9432</v>
@@ -627,10 +627,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" t="n">
+        <v>0.6818</v>
       </c>
     </row>
   </sheetData>
@@ -763,11 +761,14 @@
           <t>The system shall validate user credentials and grant access to portal functionalities upon successful authentication.</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -781,11 +782,14 @@
           <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>CF_M05_R22</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -816,6 +820,14 @@
           <t>The system shall automatically convert any mention of the old name to the new name throughout the portal and applications.</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Extracted from Use Case #06</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -829,6 +841,10 @@
           <t>Convert any mention of the old name to the new name.</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -859,6 +875,14 @@
           <t>The system shall display a list of applications to which the authenticated user has access.</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Extracted from Use Case #02</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -872,6 +896,10 @@
           <t>View the portal applications to which the user has access.</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -902,6 +930,14 @@
           <t>The system shall allow users to access applications from the portal.</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Extracted from Use Case #03</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -915,6 +951,10 @@
           <t>Access the applications to which the user has access on the portal.</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -945,6 +985,14 @@
           <t>The system shall allow users to access the portal through personal credential authentication.</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Extracted from Use Case #01</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>FR</t>
@@ -958,6 +1006,10 @@
           <t>Access the portal using credential authentication personal.</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -988,6 +1040,14 @@
           <t>The system shall ensure that users cannot access data belonging to other clients.</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Extracted from Use Case #05</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1001,6 +1061,10 @@
           <t>Ensure that other customers' data cannot be accessed.</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1031,6 +1095,14 @@
           <t>The system shall allow administrators to assign or revoke application access for users.</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Extracted from Use Case #07</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1044,6 +1116,10 @@
           <t>Give or remove access to applications from users.</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1074,6 +1150,14 @@
           <t>The system shall restrict data visualization and actions (create, modify, delete) based on the user's assigned roles.</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Extracted from Use Case #04</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1087,6 +1171,10 @@
           <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1117,11 +1205,14 @@
           <t>80% of users shall not need to ask for third-party help to use the application.</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1136,11 +1227,14 @@
 use the application.</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M05_R10</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1176,6 +1270,9 @@
           <t>C_09</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1194,11 +1291,9 @@
           <t>CF_M05_C09</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1229,11 +1324,14 @@
           <t>The learning time for new functionalities should not exceed 5 minutes.</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>R_14</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1247,11 +1345,14 @@
           <t>Learning time for new features should not exceed 5 min.</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>CF_M05_R14</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1287,6 +1388,9 @@
           <t>C_05</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1305,11 +1409,9 @@
           <t>CF_M05_C05</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1345,6 +1447,9 @@
           <t>C_08</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1364,11 +1469,9 @@
           <t>CF_M05_C08</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1399,11 +1502,14 @@
           <t>System availability must be at least 99.9%, even during peak usage times.</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1418,11 +1524,14 @@
 during times of intensive use.</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M05_R20</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1458,6 +1567,9 @@
           <t>C_04</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1476,11 +1588,9 @@
           <t>CF_M05_C04</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1511,11 +1621,14 @@
           <t>Design, colors, fonts, and organization must be consistent with the old version.</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1529,11 +1642,14 @@
           <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M05_R08</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1569,6 +1685,9 @@
           <t>C_01</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1587,11 +1706,9 @@
           <t>CF_M05_C01</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1622,11 +1739,14 @@
           <t>Response time shall not exceed 1 second in 95% of queries.</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_16</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1640,11 +1760,14 @@
           <t>Response time should not exceed 1 second in 95% of queries.</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M05_R16</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1680,6 +1803,9 @@
           <t>C_07</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1699,11 +1825,9 @@
           <t>CF_M05_C07</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1739,6 +1863,9 @@
           <t>C_06</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1758,11 +1885,9 @@
           <t>CF_M05_C06</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1798,6 +1923,9 @@
           <t>C_02</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1816,11 +1944,9 @@
           <t>CF_M05_C02</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1856,6 +1982,9 @@
           <t>C_03</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1874,11 +2003,9 @@
           <t>CF_M05_C03</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2103,18 +2230,23 @@
           <t>Criterion</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>No user can access data from other customers.</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The system shall allow users to access the portal through personal credential authentication.</t>
+          <t>The system shall ensure that users cannot access data belonging to other clients.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.8801</v>
       </c>
     </row>
     <row r="5">
